--- a/docs/addons.xlsx
+++ b/docs/addons.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -621,27 +621,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>disks</t>
+          <t>diskcompat</t>
         </is>
       </c>
       <c r="B11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Config disks related setting.</t>
+          <t>Add current drives to DSM disk compatibility data and clear unsupported-drive storage pool warnings.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>配置与磁盘相关的设置.</t>
+          <t>将当前硬盘加入 DSM 磁盘兼容性数据，并清理不支持硬盘导致的存储池风险提示。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>eudev</t>
+          <t>disks</t>
         </is>
       </c>
       <c r="B12" t="b">
@@ -649,39 +649,39 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>eudev + kmod automatically loaded modules.</t>
+          <t>Config disks related setting.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>eudev + kmod 自动加载模块.</t>
+          <t>配置与磁盘相关的设置.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>expands</t>
+          <t>eudev</t>
         </is>
       </c>
       <c r="B13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Expanded miscellaneous, updated usb.map, ca-certificates.crt, etc.</t>
+          <t>eudev + kmod automatically loaded modules.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>扩展杂项, 更新 usb.map, ca-certificates.crt 等.</t>
+          <t>eudev + kmod 自动加载模块.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>hdddb</t>
+          <t>expands</t>
         </is>
       </c>
       <c r="B14" t="b">
@@ -689,19 +689,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Author: 007revad. Add HDD/SSD drives to the DSM database to solve the problem of firmware version not recognized by the disk.</t>
+          <t>Expanded miscellaneous, updated usb.map, ca-certificates.crt, etc.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>作者: 007revad. 将HDD/SSD驱动器数据添加到DSM数据库中, 以解决硬盘固件版本无法识别的问题.</t>
+          <t>扩展杂项, 更新 usb.map, ca-certificates.crt 等.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>i915le10th</t>
+          <t>hdddb</t>
         </is>
       </c>
       <c r="B15" t="b">
@@ -709,59 +709,59 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Automatically replace the device ID of i915.ko(apollolake, geminilake), only supporting less 10th. (Parameter VID:PID)</t>
+          <t>Author: 007revad. Add HDD/SSD drives to the DSM database to solve the problem of firmware version not recognized by the disk.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">自动替换 i915.ko (apollolake, geminilake) 的设备 ID, 仅支持 10 代以下. (参数VID:PID) </t>
+          <t>作者: 007revad. 将HDD/SSD驱动器数据添加到DSM数据库中, 以解决硬盘固件版本无法识别的问题.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>localrss</t>
+          <t>i915le10th</t>
         </is>
       </c>
       <c r="B16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Implant RSS into the bootloader so that it can be installed online.</t>
+          <t>Automatically replace the device ID of i915.ko(apollolake, geminilake), only supporting less 10th. (Parameter VID:PID)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>将 RSS 植入到引导加载程序中, 以便可以在线安装.</t>
+          <t xml:space="preserve">自动替换 i915.ko (apollolake, geminilake) 的设备 ID, 仅支持 10 代以下. (参数VID:PID) </t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>lsiutil</t>
+          <t>localrss</t>
         </is>
       </c>
       <c r="B17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>A tool for working with some LSI RAID controllers.</t>
+          <t>Implant RSS into the bootloader so that it can be installed online.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>用于处理某些 LSI RAID 控制器的工具.</t>
+          <t>将 RSS 植入到引导加载程序中, 以便可以在线安装.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>maiyunda</t>
+          <t>lsiutil</t>
         </is>
       </c>
       <c r="B18" t="b">
@@ -769,59 +769,59 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Control Maiyunda M1S machine RESET button event, press and hold for 3s (release after hearing beeping) reset admin password to maiyunda.com and reset network, press and hold for 9s (release after hearing 3 beeps) reset system (all data will be erased).</t>
+          <t>A tool for working with some LSI RAID controllers.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>用于控制 迈云达M1S 机器的 RESET 按钮事件, 按住 3s (听到哔哔哔后松手) 重置 admin 密码为 maiyunda.com 并重置网络, 按住 9s (听到 3次 哔哔哔后松手) 重置系统 (会清空全部数据).</t>
+          <t>用于处理某些 LSI RAID 控制器的工具.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>maiyunda</t>
         </is>
       </c>
       <c r="B19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Miscellaneous functions. (A collection of some necessary modifications.)</t>
+          <t>Control Maiyunda M1S machine RESET button event, press and hold for 3s (release after hearing beeping) reset admin password to maiyunda.com and reset network, press and hold for 9s (release after hearing 3 beeps) reset system (all data will be erased).</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>杂项功能. (一些必要的修改的集合.)</t>
+          <t>用于控制 迈云达M1S 机器的 RESET 按钮事件, 按住 3s (听到哔哔哔后松手) 重置 admin 密码为 maiyunda.com 并重置网络, 按住 9s (听到 3次 哔哔哔后松手) 重置系统 (会清空全部数据).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>monitor</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="B20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Monitor Power Management (Only supports graphics card drivers).</t>
+          <t>Miscellaneous functions. (A collection of some necessary modifications.)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>显示器电源管理 (仅支持显卡已驱动的环境)。</t>
+          <t>杂项功能. (一些必要的修改的集合.)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>mountloader</t>
+          <t>monitor</t>
         </is>
       </c>
       <c r="B21" t="b">
@@ -829,39 +829,39 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Mount boot disk and upgrade boot script under DSM system, for rr-manager application.</t>
+          <t>Monitor Power Management (Only supports graphics card drivers).</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>在 DSM 系统下挂载引导磁盘和升级引导的脚本, 供 rr-manager 应用程序使用.</t>
+          <t>显示器电源管理 (仅支持显卡已驱动的环境)。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>netfix</t>
+          <t>mountloader</t>
         </is>
       </c>
       <c r="B22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Fix network interface mac.</t>
+          <t>Mount boot disk and upgrade boot script under DSM system, for rr-manager application.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>修复网络接口mac地址.</t>
+          <t>在 DSM 系统下挂载引导磁盘和升级引导的脚本, 供 rr-manager 应用程序使用.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>notify</t>
+          <t>netfix</t>
         </is>
       </c>
       <c r="B23" t="b">
@@ -869,39 +869,39 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Add rr notify.</t>
+          <t>Fix network interface mac.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>添加 rr notify.</t>
+          <t>修复网络接口mac地址.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>nvmecache</t>
+          <t>notify</t>
         </is>
       </c>
       <c r="B24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Author: PeterSuh-Q3. Enable NVME disk support for DS918+, DS1019+, DS1621xs+, RS1619xs+.</t>
+          <t>Add rr notify.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>作者: PeterSuh-Q3. 启用 DS918+、DS1019+、DS1621xs+、RS1619xs+ 的 NVME 硬盘支持.</t>
+          <t>添加 rr notify.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>nvmesystem</t>
+          <t>nvmecache</t>
         </is>
       </c>
       <c r="B25" t="b">
@@ -909,19 +909,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Author: jim3ma. Install system on NVME disk (can't contain any SATA disk during installation, only supports DT mdoels).</t>
+          <t>Author: PeterSuh-Q3. Enable NVME disk support for DS918+, DS1019+, DS1621xs+, RS1619xs+.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>作者: jim3ma. 在 NVME 盘上安装系统 (在安装过程中不能包含 SATA 盘，仅支持 DT 型号).</t>
+          <t>作者: PeterSuh-Q3. 启用 DS918+、DS1019+、DS1621xs+、RS1619xs+ 的 NVME 硬盘支持.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>nvmevolume</t>
+          <t>nvmesystem</t>
         </is>
       </c>
       <c r="B26" t="b">
@@ -929,19 +929,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Author: 007revad &amp; PeterSuh-Q3. Allow creation of storage pools and volumes from Storage Manager through NVME disks.</t>
+          <t>Author: jim3ma. Install system on NVME disk (can't contain any SATA disk during installation, only supports DT mdoels).</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>作者: 007revad &amp; PeterSuh-Q3. 允许从存储管理器中通过 NVME 磁盘创建存储池和卷.</t>
+          <t>作者: jim3ma. 在 NVME 盘上安装系统 (在安装过程中不能包含 SATA 盘，仅支持 DT 型号).</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>powersched</t>
+          <t>nvmevolume</t>
         </is>
       </c>
       <c r="B27" t="b">
@@ -949,19 +949,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>A program to configure the RTC according to the DSM power plan, so that the RTC (scheduled power on/off) can work properly.</t>
+          <t>Author: 007revad &amp; PeterSuh-Q3. Allow creation of storage pools and volumes from Storage Manager through NVME disks.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>根据 DSM 电源计划配置 RTC 的程序, 使 RTC(定时开关机) 可以正常工作.</t>
+          <t>作者: 007revad &amp; PeterSuh-Q3. 允许从存储管理器中通过 NVME 磁盘创建存储池和卷.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>reboottoloader</t>
+          <t>powersched</t>
         </is>
       </c>
       <c r="B28" t="b">
@@ -969,99 +969,99 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Add a script to restart to RR in the DSM scheduled task, making it easy to access RR with not have a screen and keyboard.</t>
+          <t>A program to configure the RTC according to the DSM power plan, so that the RTC (scheduled power on/off) can work properly.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>在 DSM 计划任务中添加一个脚本以重新启动到 RR, 这使得很容易访问 RR 而不需要屏幕和键盘.</t>
+          <t>根据 DSM 电源计划配置 RTC 的程序, 使 RTC(定时开关机) 可以正常工作.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>redpill</t>
+          <t>reboottoloader</t>
         </is>
       </c>
       <c r="B29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Delay redpill.</t>
+          <t>Add a script to restart to RR in the DSM scheduled task, making it easy to access RR with not have a screen and keyboard.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>延迟 redpill.</t>
+          <t>在 DSM 计划任务中添加一个脚本以重新启动到 RR, 这使得很容易访问 RR 而不需要屏幕和键盘.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>remotefs</t>
+          <t>redpill</t>
         </is>
       </c>
       <c r="B30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Author: jinlife. This patch will allow remote NFS/CIFS shared folder be used in VideoStation, AudioStation and Photos etc.</t>
+          <t>Delay redpill.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>作者: jinlife. 此补丁将允许在 VideoStation、AudioStation 和 Photos 等应用中使用远程 NFS/CIFS 共享文件夹.</t>
+          <t>延迟 redpill.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>revert</t>
+          <t>remotefs</t>
         </is>
       </c>
       <c r="B31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Revert addons modifications.</t>
+          <t>Author: jinlife. This patch will allow remote NFS/CIFS shared folder be used in VideoStation, AudioStation and Photos etc.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>撤销插件修改.</t>
+          <t>作者: jinlife. 此补丁将允许在 VideoStation、AudioStation 和 Photos 等应用中使用远程 NFS/CIFS 共享文件夹.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>sensors</t>
+          <t>revert</t>
         </is>
       </c>
       <c r="B32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>This script installs the sensors and fancontrol tools for CPU monitoring and fan control, which can be adjusted through the Fancontrol in the scheduled task.</t>
+          <t>Revert addons modifications.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>此脚本安装 sensors 和 fancontrol 工具, 用于监视 CPU 和风扇控制, 可通过计划任务中 Fancontrol 调整风扇具体参数.</t>
+          <t>撤销插件修改.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>setrootpw</t>
+          <t>sensors</t>
         </is>
       </c>
       <c r="B33" t="b">
@@ -1069,19 +1069,19 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Set root password and enable ssh/sftp. Please modify PW='' to the desired password in DSM Task Scheduler and run the task.</t>
+          <t>This script installs the sensors and fancontrol tools for CPU monitoring and fan control, which can be adjusted through the Fancontrol in the scheduled task.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>设置 root 密码并启用 ssh/sftp. 请在 DSM 计划任务中将 PW='' 修改为所需的密码并运行该任务.</t>
+          <t>此脚本安装 sensors 和 fancontrol 工具, 用于监视 CPU 和风扇控制, 可通过计划任务中 Fancontrol 调整风扇具体参数.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>smartctl</t>
+          <t>setrootpw</t>
         </is>
       </c>
       <c r="B34" t="b">
@@ -1089,19 +1089,19 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Author: Phachd. Fix SMART information on disks on HBA devices.</t>
+          <t>Set root password and enable ssh/sftp. Please modify PW='' to the desired password in DSM Task Scheduler and run the task.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>作者: Phachd. 修复 HBA 设备上磁盘的 SMART 信息.</t>
+          <t>设置 root 密码并启用 ssh/sftp. 请在 DSM 计划任务中将 PW='' 修改为所需的密码并运行该任务.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>sortnetif</t>
+          <t>smartctl</t>
         </is>
       </c>
       <c r="B35" t="b">
@@ -1109,19 +1109,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sort network interface name.(parameters: empty: sorted by busid; mac1,mac2,...: sorted by macs sequence).</t>
+          <t>Author: Phachd. Fix SMART information on disks on HBA devices.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>对网络接口名称进行排序. (参数: 空: 按 busid 排序; mac1,mac2,...: 按 macs 序列排序).</t>
+          <t>作者: Phachd. 修复 HBA 设备上磁盘的 SMART 信息.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>storagepanel</t>
+          <t>sortnetif</t>
         </is>
       </c>
       <c r="B36" t="b">
@@ -1129,19 +1129,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Change the storage panel disk display (The default is automatic, please see the documentation or '/usr/bin/storagepanel.sh -h' for parameters).</t>
+          <t>Sort network interface name.(parameters: empty: sorted by busid; mac1,mac2,...: sorted by macs sequence).</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>更改存储面板磁盘显示 (默认为自动, 请参阅文档或 '/usr/bin/storagepanel.sh -h' 了解参数).</t>
+          <t>对网络接口名称进行排序. (参数: 空: 按 busid 排序; mac1,mac2,...: 按 macs 序列排序).</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>synoconfbkp</t>
+          <t>storagepanel</t>
         </is>
       </c>
       <c r="B37" t="b">
@@ -1149,19 +1149,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Automatically backup system config settings to the bootloader disk(&lt;loader disk&gt;/p1/scbk/) at bootup and shutdown. Parameters: $1 - number of saves, default 7; $2 - file name prefix, default 'bkp'.</t>
+          <t>Change the storage panel disk display (The default is automatic, please see the documentation or '/usr/bin/storagepanel.sh -h' for parameters).</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>在启动和关机时自动备份系统配置设置到引导加载器磁盘 (&lt;引导加载器磁盘&gt;/p1/scbk/). 参数: $1 - 保存次数, 默认 7; $2 - 文件名前缀, 默认 'bkp'.</t>
+          <t>更改存储面板磁盘显示 (默认为自动, 请参阅文档或 '/usr/bin/storagepanel.sh -h' 了解参数).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>tad6s4n10g</t>
+          <t>synoconfbkp</t>
         </is>
       </c>
       <c r="B38" t="b">
@@ -1169,19 +1169,19 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Control TANK TAD6S4N10G machine DTS generation and button events, please modify the content of the Net-Button-3s Net-Button-9s Copy-Button-3s Copy-Button-9s tasks in the scheduled tasks.</t>
+          <t>Automatically backup system config settings to the bootloader disk(&lt;loader disk&gt;/p1/scbk/) at bootup and shutdown. Parameters: $1 - number of saves, default 7; $2 - file name prefix, default 'bkp'.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>用于控制TANK TAD6S4N10G 机器的 DTS 生成 和 按钮事件, 事件内容请自行修改 计划任务中 Net-Button-3s Net-Button-9s Copy-Button-3s Copy-Button-9s 几个任务的内容.</t>
+          <t>在启动和关机时自动备份系统配置设置到引导加载器磁盘 (&lt;引导加载器磁盘&gt;/p1/scbk/). 参数: $1 - 保存次数, 默认 7; $2 - 文件名前缀, 默认 'bkp'.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>trivial</t>
+          <t>tad6s4n10g</t>
         </is>
       </c>
       <c r="B39" t="b">
@@ -1189,19 +1189,19 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Miscellaneous functions. (A collection of some unnecessary modifications.)</t>
+          <t>Control TANK TAD6S4N10G machine DTS generation and button events, please modify the content of the Net-Button-3s Net-Button-9s Copy-Button-3s Copy-Button-9s tasks in the scheduled tasks.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>杂项功能. (一些不太必要的修改的集合.)</t>
+          <t>用于控制TANK TAD6S4N10G 机器的 DTS 生成 和 按钮事件, 事件内容请自行修改 计划任务中 Net-Button-3s Net-Button-9s Copy-Button-3s Copy-Button-9s 几个任务的内容.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>updatenotify</t>
+          <t>trivial</t>
         </is>
       </c>
       <c r="B40" t="b">
@@ -1209,19 +1209,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>RR update notification.</t>
+          <t>Miscellaneous functions. (A collection of some unnecessary modifications.)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>RR 更新通知.</t>
+          <t>杂项功能. (一些不太必要的修改的集合.)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ups</t>
+          <t>updatenotify</t>
         </is>
       </c>
       <c r="B41" t="b">
@@ -1229,19 +1229,19 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Author: GXNAS. Force the standby mode to shutdown when UPS power supply. Parameters: -f - Trigger shutdown task before shutdown; -e - Trigger shutdown task before standby mode (not change to shutdown).</t>
+          <t>RR update notification.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>作者: GXNAS. 强制将 UPS 供电时的待机模式修改为关机. 參數: -f - 关机前触发关机任务; -e - 待机模式前发关机任务(不修改为关机).</t>
+          <t>RR 更新通知.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>virtiofs</t>
+          <t>ups</t>
         </is>
       </c>
       <c r="B42" t="b">
@@ -1249,19 +1249,19 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Auto mount virtio9p and virtiofs file systems (effective after rebooting the system after creating the storage space for the first time since it is mounted to the first storage space by default).</t>
+          <t>Author: GXNAS. Force the standby mode to shutdown when UPS power supply. Parameters: -f - Trigger shutdown task before shutdown; -e - Trigger shutdown task before standby mode (not change to shutdown).</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>自动挂载 virtio9p 和 virtiofs 文件系统(由于默认挂载到第一个存储空间，所以首次安装系统创建存储空间后重启生效).</t>
+          <t>作者: GXNAS. 强制将 UPS 供电时的待机模式修改为关机. 參數: -f - 关机前触发关机任务; -e - 待机模式前发关机任务(不修改为关机).</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>vmtools</t>
+          <t>virtiofs</t>
         </is>
       </c>
       <c r="B43" t="b">
@@ -1269,19 +1269,19 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Automatically install qemu-ga or open-vm-tools according to the environment. (Physical machines are not enabled by default, no need to cancel)</t>
+          <t>Auto mount virtio9p and virtiofs file systems (effective after rebooting the system after creating the storage space for the first time since it is mounted to the first storage space by default).</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>根据环境自动安装 qemu-ga 或者 open-vm-tools. (物理机默认不会启用, 不需要取消)</t>
+          <t>自动挂载 virtio9p 和 virtiofs 文件系统(由于默认挂载到第一个存储空间，所以首次安装系统创建存储空间后重启生效).</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>wireless</t>
+          <t>vmtools</t>
         </is>
       </c>
       <c r="B44" t="b">
@@ -1289,30 +1289,50 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Connect WiFi. Please modify 'IFNAME' 'SSID' 'PASSWD' to the required password in the DSM scheduled task and execute it.</t>
+          <t>Automatically install qemu-ga or open-vm-tools according to the environment. (Physical machines are not enabled by default, no need to cancel)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>连接 WiFi. 请在 DSM 计划任务中将 'IFNAME' 'SSID' 'PASSWD' 修改为所需密码并执行它.</t>
+          <t>根据环境自动安装 qemu-ga 或者 open-vm-tools. (物理机默认不会启用, 不需要取消)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>wireless</t>
+        </is>
+      </c>
+      <c r="B45" t="b">
+        <v>0</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Connect WiFi. Please modify 'IFNAME' 'SSID' 'PASSWD' to the required password in the DSM scheduled task and execute it.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>连接 WiFi. 请在 DSM 计划任务中将 'IFNAME' 'SSID' 'PASSWD' 修改为所需密码并执行它.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>wol</t>
         </is>
       </c>
-      <c r="B45" t="b">
+      <c r="B46" t="b">
         <v>1</v>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Force enable Wake-on-lan for network devices.</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>强制启用网络设备的 Wake-on-lan.</t>
         </is>

--- a/docs/addons.xlsx
+++ b/docs/addons.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1221,7 +1221,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>updatenotify</t>
+          <t>updatehosts</t>
         </is>
       </c>
       <c r="B41" t="b">
@@ -1229,19 +1229,19 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>RR update notification.</t>
+          <t>Update hosts file for synology domain (can add other domain).</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>RR 更新通知.</t>
+          <t>更新 synology 域的 hosts 文件(可自行添加其他域)。</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ups</t>
+          <t>updatenotify</t>
         </is>
       </c>
       <c r="B42" t="b">
@@ -1249,19 +1249,19 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Author: GXNAS. Force the standby mode to shutdown when UPS power supply. Parameters: -f - Trigger shutdown task before shutdown; -e - Trigger shutdown task before standby mode (not change to shutdown).</t>
+          <t>RR update notification.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>作者: GXNAS. 强制将 UPS 供电时的待机模式修改为关机. 參數: -f - 关机前触发关机任务; -e - 待机模式前发关机任务(不修改为关机).</t>
+          <t>RR 更新通知.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>virtiofs</t>
+          <t>ups</t>
         </is>
       </c>
       <c r="B43" t="b">
@@ -1269,19 +1269,19 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Auto mount virtio9p and virtiofs file systems (effective after rebooting the system after creating the storage space for the first time since it is mounted to the first storage space by default).</t>
+          <t>Author: GXNAS. Force the standby mode to shutdown when UPS power supply. Parameters: -f - Trigger shutdown task before shutdown; -e - Trigger shutdown task before standby mode (not change to shutdown).</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>自动挂载 virtio9p 和 virtiofs 文件系统(由于默认挂载到第一个存储空间，所以首次安装系统创建存储空间后重启生效).</t>
+          <t>作者: GXNAS. 强制将 UPS 供电时的待机模式修改为关机. 參數: -f - 关机前触发关机任务; -e - 待机模式前发关机任务(不修改为关机).</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>vmtools</t>
+          <t>virtiofs</t>
         </is>
       </c>
       <c r="B44" t="b">
@@ -1289,19 +1289,19 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Automatically install qemu-ga or open-vm-tools according to the environment. (Physical machines are not enabled by default, no need to cancel)</t>
+          <t>Auto mount virtio9p and virtiofs file systems (effective after rebooting the system after creating the storage space for the first time since it is mounted to the first storage space by default).</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>根据环境自动安装 qemu-ga 或者 open-vm-tools. (物理机默认不会启用, 不需要取消)</t>
+          <t>自动挂载 virtio9p 和 virtiofs 文件系统(由于默认挂载到第一个存储空间，所以首次安装系统创建存储空间后重启生效).</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>wireless</t>
+          <t>vmtools</t>
         </is>
       </c>
       <c r="B45" t="b">
@@ -1309,30 +1309,50 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Connect WiFi. Please modify 'IFNAME' 'SSID' 'PASSWD' to the required password in the DSM scheduled task and execute it.</t>
+          <t>Automatically install qemu-ga or open-vm-tools according to the environment. (Physical machines are not enabled by default, no need to cancel)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>连接 WiFi. 请在 DSM 计划任务中将 'IFNAME' 'SSID' 'PASSWD' 修改为所需密码并执行它.</t>
+          <t>根据环境自动安装 qemu-ga 或者 open-vm-tools. (物理机默认不会启用, 不需要取消)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>wireless</t>
+        </is>
+      </c>
+      <c r="B46" t="b">
+        <v>0</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Connect WiFi. Please modify 'IFNAME' 'SSID' 'PASSWD' to the required password in the DSM scheduled task and execute it.</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>连接 WiFi. 请在 DSM 计划任务中将 'IFNAME' 'SSID' 'PASSWD' 修改为所需密码并执行它.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>wol</t>
         </is>
       </c>
-      <c r="B46" t="b">
+      <c r="B47" t="b">
         <v>1</v>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Force enable Wake-on-lan for network devices.</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>强制启用网络设备的 Wake-on-lan.</t>
         </is>
